--- a/notebooks/paper_2025/table_3.xlsx
+++ b/notebooks/paper_2025/table_3.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,10 +372,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_individ</t>
         </is>
@@ -400,8 +405,13 @@
       <c r="D2">
         <v>0.8</v>
       </c>
-      <c r="E2">
-        <v>233</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>234</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +427,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D3">
         <v>0.8</v>
       </c>
-      <c r="E3">
-        <v>194</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>228</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +455,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D4">
         <v>0.8</v>
       </c>
-      <c r="E4">
-        <v>351</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>233</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +483,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D5">
         <v>0.8</v>
       </c>
-      <c r="E5">
-        <v>303</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>194</v>
       </c>
     </row>
     <row r="6">
@@ -486,14 +511,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D6">
-        <v>0.9</v>
-      </c>
-      <c r="E6">
-        <v>363</v>
+        <v>0.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -513,10 +543,15 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.9</v>
-      </c>
-      <c r="E7">
-        <v>314</v>
+        <v>0.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -536,10 +571,15 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.9</v>
-      </c>
-      <c r="E8">
-        <v>516</v>
+        <v>0.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -555,14 +595,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D9">
-        <v>0.9</v>
-      </c>
-      <c r="E9">
-        <v>462</v>
+        <v>0.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -573,19 +618,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D10">
         <v>0.8</v>
       </c>
-      <c r="E10">
-        <v>52</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -596,19 +646,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D11">
         <v>0.8</v>
       </c>
-      <c r="E11">
-        <v>33</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>306</v>
       </c>
     </row>
     <row r="12">
@@ -619,19 +674,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D12">
         <v>0.8</v>
       </c>
-      <c r="E12">
-        <v>67</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>303</v>
       </c>
     </row>
     <row r="13">
@@ -642,7 +702,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -653,8 +713,13 @@
       <c r="D13">
         <v>0.8</v>
       </c>
-      <c r="E13">
-        <v>51</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>308</v>
       </c>
     </row>
     <row r="14">
@@ -665,7 +730,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -676,8 +741,13 @@
       <c r="D14">
         <v>0.9</v>
       </c>
-      <c r="E14">
-        <v>67</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>355</v>
       </c>
     </row>
     <row r="15">
@@ -688,19 +758,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D15">
         <v>0.9</v>
       </c>
-      <c r="E15">
-        <v>46</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>356</v>
       </c>
     </row>
     <row r="16">
@@ -711,19 +786,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D16">
         <v>0.9</v>
       </c>
-      <c r="E16">
-        <v>87</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>349</v>
       </c>
     </row>
     <row r="17">
@@ -734,19 +814,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ascaris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D17">
         <v>0.9</v>
       </c>
-      <c r="E17">
-        <v>67</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>315</v>
       </c>
     </row>
     <row r="18">
@@ -757,19 +842,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D18">
-        <v>0.8</v>
-      </c>
-      <c r="E18">
-        <v>5532</v>
+        <v>0.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>307</v>
       </c>
     </row>
     <row r="19">
@@ -780,7 +870,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -789,10 +879,15 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.8</v>
-      </c>
-      <c r="E19">
-        <v>5493</v>
+        <v>0.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>307</v>
       </c>
     </row>
     <row r="20">
@@ -803,7 +898,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -812,10 +907,15 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.8</v>
-      </c>
-      <c r="E20">
-        <v>6841</v>
+        <v>0.9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>506</v>
       </c>
     </row>
     <row r="21">
@@ -826,19 +926,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D21">
-        <v>0.8</v>
-      </c>
-      <c r="E21">
-        <v>6749</v>
+        <v>0.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>511</v>
       </c>
     </row>
     <row r="22">
@@ -849,19 +954,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D22">
         <v>0.9</v>
       </c>
-      <c r="E22">
-        <v>7363</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>508</v>
       </c>
     </row>
     <row r="23">
@@ -872,19 +982,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D23">
         <v>0.9</v>
       </c>
-      <c r="E23">
-        <v>7221</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>460</v>
       </c>
     </row>
     <row r="24">
@@ -895,19 +1010,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D24">
         <v>0.9</v>
       </c>
-      <c r="E24">
-        <v>9144</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>455</v>
       </c>
     </row>
     <row r="25">
@@ -918,7 +1038,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>hookworm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -929,19 +1049,24 @@
       <c r="D25">
         <v>0.9</v>
       </c>
-      <c r="E25">
-        <v>8914</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>461</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -952,111 +1077,136 @@
       <c r="D26">
         <v>0.8</v>
       </c>
-      <c r="E26">
-        <v>2891</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D27">
         <v>0.8</v>
       </c>
-      <c r="E27">
-        <v>2820</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D28">
         <v>0.8</v>
       </c>
-      <c r="E28">
-        <v>3596</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D29">
         <v>0.8</v>
       </c>
-      <c r="E29">
-        <v>3594</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D30">
-        <v>0.9</v>
-      </c>
-      <c r="E30">
-        <v>3948</v>
+        <v>0.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1065,21 +1215,26 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.9</v>
-      </c>
-      <c r="E31">
-        <v>3714</v>
+        <v>0.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1088,39 +1243,49 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.9</v>
-      </c>
-      <c r="E32">
-        <v>4920</v>
+        <v>0.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hookworm</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D33">
-        <v>0.9</v>
-      </c>
-      <c r="E33">
-        <v>4789</v>
+        <v>0.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1130,20 +1295,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D34">
         <v>0.8</v>
       </c>
-      <c r="E34">
-        <v>206</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1153,20 +1323,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D35">
         <v>0.8</v>
       </c>
-      <c r="E35">
-        <v>197</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1176,20 +1351,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D36">
         <v>0.8</v>
       </c>
-      <c r="E36">
-        <v>259</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1205,14 +1385,19 @@
       <c r="D37">
         <v>0.8</v>
       </c>
-      <c r="E37">
-        <v>255</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1228,14 +1413,19 @@
       <c r="D38">
         <v>0.9</v>
       </c>
-      <c r="E38">
-        <v>341</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1245,20 +1435,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D39">
         <v>0.9</v>
       </c>
-      <c r="E39">
-        <v>333</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1268,20 +1463,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>NS_11</t>
         </is>
       </c>
       <c r="D40">
         <v>0.9</v>
       </c>
-      <c r="E40">
-        <v>416</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1291,48 +1491,58 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D41">
         <v>0.9</v>
       </c>
-      <c r="E41">
-        <v>419</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>NS_12</t>
         </is>
       </c>
       <c r="D42">
-        <v>0.8</v>
-      </c>
-      <c r="E42">
-        <v>6007</v>
+        <v>0.9</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1341,21 +1551,26 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.8</v>
-      </c>
-      <c r="E43">
-        <v>5908</v>
+        <v>0.9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1364,113 +1579,138 @@
         </is>
       </c>
       <c r="D44">
-        <v>0.8</v>
-      </c>
-      <c r="E44">
-        <v>7423</v>
+        <v>0.9</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SSR_12</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D45">
-        <v>0.8</v>
-      </c>
-      <c r="E45">
-        <v>7452</v>
+        <v>0.9</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NS_11</t>
+          <t>SSR_11</t>
         </is>
       </c>
       <c r="D46">
         <v>0.9</v>
       </c>
-      <c r="E46">
-        <v>7929</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NS_12</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D47">
         <v>0.9</v>
       </c>
-      <c r="E47">
-        <v>7755</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SSR_11</t>
+          <t>SSR_12</t>
         </is>
       </c>
       <c r="D48">
         <v>0.9</v>
       </c>
-      <c r="E48">
-        <v>9916</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>trichuris</t>
+          <t>ascaris</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1481,8 +1721,2701 @@
       <c r="D49">
         <v>0.9</v>
       </c>
-      <c r="E49">
-        <v>9712</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F49">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>0.8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>5578</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>0.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F51">
+        <v>5588</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>0.8</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F52">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>0.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F53">
+        <v>5456</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>0.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F54">
+        <v>5458</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>0.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F55">
+        <v>5395</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>0.8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>6887</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>0.8</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F57">
+        <v>7015</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>0.8</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F58">
+        <v>6945</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>0.8</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F59">
+        <v>6657</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>0.8</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F60">
+        <v>6664</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>0.8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F61">
+        <v>6661</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>0.9</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F62">
+        <v>7268</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>0.9</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F63">
+        <v>7274</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>0.9</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F64">
+        <v>7357</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>0.9</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F65">
+        <v>7154</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>0.9</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F66">
+        <v>7151</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>0.9</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F67">
+        <v>7030</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>0.9</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F68">
+        <v>9108</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>0.9</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F69">
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>0.9</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F70">
+        <v>9244</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>0.9</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F71">
+        <v>8731</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>0.9</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F72">
+        <v>8810</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>0.9</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F73">
+        <v>8825</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>0.8</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F74">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>0.8</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F75">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>0.8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F76">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>0.8</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F77">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>0.8</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F78">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>0.8</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F79">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>0.8</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F80">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>0.8</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>0.8</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>0.8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F83">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>0.8</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F84">
+        <v>3548</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>0.8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F85">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>0.9</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F86">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>0.9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F87">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>0.9</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F88">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>0.9</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F89">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>0.9</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F90">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>0.9</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F91">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>0.9</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F92">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>0.9</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F93">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>0.9</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F94">
+        <v>5013</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>0.9</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F95">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>0.9</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F96">
+        <v>4839</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hookworm</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>0.9</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F97">
+        <v>4917</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>0.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F98">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>0.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F99">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>0.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F100">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>0.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F101">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>0.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F102">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D103">
+        <v>0.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F103">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D104">
+        <v>0.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F104">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D105">
+        <v>0.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F105">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>0.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F106">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D107">
+        <v>0.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F107">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>0.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F108">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D109">
+        <v>0.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F109">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>0.9</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F110">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>0.9</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F111">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D112">
+        <v>0.9</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F112">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D113">
+        <v>0.9</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F113">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D114">
+        <v>0.9</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F114">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D115">
+        <v>0.9</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F115">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D116">
+        <v>0.9</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F116">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>0.9</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F117">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>0.9</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F118">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>0.9</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F119">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>0.9</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F120">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ascaris</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>0.9</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F121">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D122">
+        <v>0.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F122">
+        <v>6028</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D123">
+        <v>0.8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F123">
+        <v>6026</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D124">
+        <v>0.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F124">
+        <v>6098</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D125">
+        <v>0.8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F125">
+        <v>6059</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D126">
+        <v>0.8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F126">
+        <v>5868</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D127">
+        <v>0.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F127">
+        <v>5901</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D128">
+        <v>0.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F128">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D129">
+        <v>0.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F129">
+        <v>7440</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D130">
+        <v>0.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F130">
+        <v>7511</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D131">
+        <v>0.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F131">
+        <v>7432</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D132">
+        <v>0.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F132">
+        <v>7321</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D133">
+        <v>0.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F133">
+        <v>7321</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D134">
+        <v>0.9</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F134">
+        <v>7853</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D135">
+        <v>0.9</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F135">
+        <v>7851</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
+      </c>
+      <c r="D136">
+        <v>0.9</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F136">
+        <v>8021</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D137">
+        <v>0.9</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F137">
+        <v>7785</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D138">
+        <v>0.9</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F138">
+        <v>7751</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>NS_12</t>
+        </is>
+      </c>
+      <c r="D139">
+        <v>0.9</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F139">
+        <v>7767</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D140">
+        <v>0.9</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F140">
+        <v>9901</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D141">
+        <v>0.9</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F141">
+        <v>9833</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SSR_11</t>
+        </is>
+      </c>
+      <c r="D142">
+        <v>0.9</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F142">
+        <v>9970</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D143">
+        <v>0.9</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F143">
+        <v>9749</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D144">
+        <v>0.9</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F144">
+        <v>9728</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>trichuris</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
+      </c>
+      <c r="D145">
+        <v>0.9</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F145">
+        <v>9728</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/paper_2025/table_3.xlsx
+++ b/notebooks/paper_2025/table_3.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,27 +367,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NS_11</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>NS_12</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SSR_11</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SSR_12</t>
+          <t>n_individ</t>
         </is>
       </c>
     </row>
@@ -402,20 +387,13 @@
           <t>hookworm</t>
         </is>
       </c>
-      <c r="C2">
-        <v>0.8</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
       </c>
       <c r="D2">
-        <v>235</v>
-      </c>
-      <c r="E2">
-        <v>195</v>
-      </c>
-      <c r="F2">
-        <v>350</v>
-      </c>
-      <c r="G2">
-        <v>310</v>
+        <v>615</v>
       </c>
     </row>
     <row r="3">
@@ -429,20 +407,13 @@
           <t>hookworm</t>
         </is>
       </c>
-      <c r="C3">
-        <v>0.9</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
       </c>
       <c r="D3">
-        <v>355</v>
-      </c>
-      <c r="E3">
-        <v>310</v>
-      </c>
-      <c r="F3">
-        <v>510</v>
-      </c>
-      <c r="G3">
-        <v>460</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4">
@@ -456,20 +427,13 @@
           <t>ascaris</t>
         </is>
       </c>
-      <c r="C4">
-        <v>0.8</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
       </c>
       <c r="D4">
-        <v>55</v>
-      </c>
-      <c r="E4">
-        <v>35</v>
-      </c>
-      <c r="F4">
-        <v>70</v>
-      </c>
-      <c r="G4">
-        <v>50</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5">
@@ -483,20 +447,13 @@
           <t>ascaris</t>
         </is>
       </c>
-      <c r="C5">
-        <v>0.9</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
       </c>
       <c r="D5">
-        <v>70</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
-      </c>
-      <c r="F5">
-        <v>90</v>
-      </c>
-      <c r="G5">
-        <v>70</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6">
@@ -510,20 +467,13 @@
           <t>trichuris</t>
         </is>
       </c>
-      <c r="C6">
-        <v>0.8</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
       </c>
       <c r="D6">
-        <v>5585</v>
-      </c>
-      <c r="E6">
-        <v>5440</v>
-      </c>
-      <c r="F6">
-        <v>6950</v>
-      </c>
-      <c r="G6">
-        <v>6665</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7">
@@ -537,20 +487,13 @@
           <t>trichuris</t>
         </is>
       </c>
-      <c r="C7">
-        <v>0.9</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
       </c>
       <c r="D7">
-        <v>7300</v>
-      </c>
-      <c r="E7">
-        <v>7115</v>
-      </c>
-      <c r="F7">
-        <v>9200</v>
-      </c>
-      <c r="G7">
-        <v>8790</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
@@ -564,20 +507,13 @@
           <t>hookworm</t>
         </is>
       </c>
-      <c r="C8">
-        <v>0.8</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
       </c>
       <c r="D8">
-        <v>2915</v>
-      </c>
-      <c r="E8">
-        <v>2840</v>
-      </c>
-      <c r="F8">
-        <v>3625</v>
-      </c>
-      <c r="G8">
-        <v>3575</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9">
@@ -591,20 +527,13 @@
           <t>hookworm</t>
         </is>
       </c>
-      <c r="C9">
-        <v>0.9</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
       </c>
       <c r="D9">
-        <v>3980</v>
-      </c>
-      <c r="E9">
-        <v>3820</v>
-      </c>
-      <c r="F9">
-        <v>5000</v>
-      </c>
-      <c r="G9">
-        <v>4870</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10">
@@ -618,20 +547,13 @@
           <t>ascaris</t>
         </is>
       </c>
-      <c r="C10">
-        <v>0.8</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
       </c>
       <c r="D10">
-        <v>205</v>
-      </c>
-      <c r="E10">
-        <v>195</v>
-      </c>
-      <c r="F10">
-        <v>255</v>
-      </c>
-      <c r="G10">
-        <v>250</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
@@ -645,20 +567,13 @@
           <t>ascaris</t>
         </is>
       </c>
-      <c r="C11">
-        <v>0.9</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
       </c>
       <c r="D11">
-        <v>335</v>
-      </c>
-      <c r="E11">
-        <v>335</v>
-      </c>
-      <c r="F11">
-        <v>415</v>
-      </c>
-      <c r="G11">
-        <v>415</v>
+        <v>855</v>
       </c>
     </row>
     <row r="12">
@@ -672,20 +587,13 @@
           <t>trichuris</t>
         </is>
       </c>
-      <c r="C12">
-        <v>0.8</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NS_11</t>
+        </is>
       </c>
       <c r="D12">
-        <v>6055</v>
-      </c>
-      <c r="E12">
-        <v>5945</v>
-      </c>
-      <c r="F12">
-        <v>7485</v>
-      </c>
-      <c r="G12">
-        <v>7360</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13">
@@ -699,20 +607,13 @@
           <t>trichuris</t>
         </is>
       </c>
-      <c r="C13">
-        <v>0.9</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SSR_12</t>
+        </is>
       </c>
       <c r="D13">
-        <v>7910</v>
-      </c>
-      <c r="E13">
-        <v>7770</v>
-      </c>
-      <c r="F13">
-        <v>9905</v>
-      </c>
-      <c r="G13">
-        <v>9735</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
